--- a/5_RTM(Requirement Traceability Matrix)/RTM.xlsx
+++ b/5_RTM(Requirement Traceability Matrix)/RTM.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>Req_ID</t>
   </si>
@@ -94,13 +94,16 @@
   </si>
   <si>
     <t>TC_21</t>
+  </si>
+  <si>
+    <t>RTM()</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,8 +119,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u val="double"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Algerian"/>
+      <family val="5"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -127,6 +137,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -143,13 +159,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -452,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:D11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -461,120 +480,132 @@
     <col min="4" max="4" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:4" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
